--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BASKONIA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BASKONIA.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>12.3767</v>
+        <v>12.6434</v>
       </c>
       <c r="E2" t="n">
-        <v>10.74</v>
+        <v>11.717</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6368</v>
+        <v>0.9263999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2658</v>
+        <v>5.5075</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9943</v>
+        <v>2.0979</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2715</v>
+        <v>3.4096</v>
       </c>
       <c r="J2" t="n">
-        <v>8.4793</v>
+        <v>9.216100000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2192</v>
+        <v>2.6252</v>
       </c>
       <c r="L2" t="n">
-        <v>6.26</v>
+        <v>6.5909</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.2134</v>
+        <v>-3.7087</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2249</v>
+        <v>-0.5273</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.9885</v>
+        <v>-3.1813</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R2" t="n">
-        <v>4.2012</v>
+        <v>4.089399999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1914</v>
+        <v>0.1611</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1174000000000001</v>
+        <v>-0.0534</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3089000000000001</v>
+        <v>0.2146</v>
       </c>
       <c r="V2" t="n">
-        <v>4.7188</v>
+        <v>4.8326</v>
       </c>
       <c r="W2" t="n">
-        <v>4.3787</v>
+        <v>4.5016</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3401</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8049</v>
+        <v>5.9331</v>
       </c>
       <c r="E3" t="n">
-        <v>4.031</v>
+        <v>4.697799999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7738</v>
+        <v>1.2352</v>
       </c>
       <c r="G3" t="n">
-        <v>6.670299999999999</v>
+        <v>6.7696</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6594</v>
+        <v>5.898300000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>1.0109</v>
+        <v>0.8713</v>
       </c>
       <c r="J3" t="n">
-        <v>5.9764</v>
+        <v>6.445499999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>5.5765</v>
+        <v>6.0403</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4</v>
+        <v>0.4053</v>
       </c>
       <c r="M3" t="n">
-        <v>0.694</v>
+        <v>0.3241000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08299999999999999</v>
+        <v>-0.1418</v>
       </c>
       <c r="O3" t="n">
-        <v>0.611</v>
+        <v>0.466</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6002000000000001</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R3" t="n">
-        <v>3.4009</v>
+        <v>3.3105</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7752</v>
+        <v>1.7339</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2966</v>
+        <v>2.3018</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5214</v>
+        <v>-0.5679</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.0406</v>
+        <v>-1.9863</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.2409</v>
+        <v>-0.1547</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9331</v>
+        <v>4.7692</v>
       </c>
       <c r="E4" t="n">
-        <v>3.549</v>
+        <v>3.7971</v>
       </c>
       <c r="F4" t="n">
-        <v>1.384</v>
+        <v>0.9721</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4106</v>
+        <v>2.3076</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8004</v>
+        <v>3.788</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3899</v>
+        <v>-1.4804</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6427</v>
+        <v>3.7915</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8028</v>
+        <v>2.9405</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8399000000000001</v>
+        <v>0.851</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2322</v>
+        <v>-1.4839</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9976</v>
+        <v>0.8475</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.2298</v>
+        <v>-2.3314</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.8005</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9626</v>
+        <v>2.89</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7077</v>
+        <v>2.6792</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2549</v>
+        <v>0.2108</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3604</v>
+        <v>1.3242</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1606</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>4.7684</v>
+        <v>4.7498</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6700999999999999</v>
+        <v>0.9914999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0982</v>
+        <v>3.7583</v>
       </c>
       <c r="G5" t="n">
-        <v>5.2806</v>
+        <v>5.2615</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3685</v>
+        <v>3.414</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9122</v>
+        <v>1.8475</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1065</v>
+        <v>3.3047</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3066</v>
+        <v>2.4941</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7998999999999999</v>
+        <v>0.8106</v>
       </c>
       <c r="M5" t="n">
-        <v>2.1741</v>
+        <v>1.9568</v>
       </c>
       <c r="N5" t="n">
-        <v>1.062</v>
+        <v>0.9199000000000002</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1123</v>
+        <v>1.0369</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2004</v>
+        <v>1.1684</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2007</v>
+        <v>2.1421</v>
       </c>
       <c r="S5" t="n">
-        <v>0.328</v>
+        <v>0.3062</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3447</v>
+        <v>0.3673</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.01669999999999999</v>
+        <v>-0.06110000000000002</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.0406</v>
+        <v>-1.9863</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.7808</v>
+        <v>-1.7068</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6983</v>
+        <v>2.7538</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2522</v>
+        <v>2.9769</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4460999999999999</v>
+        <v>-0.2231000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>4.249499999999999</v>
+        <v>4.231</v>
       </c>
       <c r="H6" t="n">
-        <v>4.988799999999999</v>
+        <v>5.0207</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7394000000000001</v>
+        <v>-0.7897000000000003</v>
       </c>
       <c r="J6" t="n">
-        <v>5.7988</v>
+        <v>6.2462</v>
       </c>
       <c r="K6" t="n">
-        <v>5.8274</v>
+        <v>6.1401</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.02860000000000007</v>
+        <v>0.1061</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5493</v>
+        <v>-2.0153</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8385</v>
+        <v>-1.1195</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7108</v>
+        <v>-0.8958</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.0002</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.0014</v>
+        <v>-4.868399999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>4.0011</v>
+        <v>3.8948</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.7507</v>
+        <v>-1.7245</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.5446</v>
+        <v>-1.4536</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2061</v>
+        <v>-0.2709</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="W6" t="n">
-        <v>2.9995</v>
+        <v>3.0527</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7997</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3763000000000001</v>
+        <v>0.1925999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9143000000000001</v>
+        <v>-0.8088</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2906</v>
+        <v>1.0015</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1928</v>
+        <v>2.0715</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2632</v>
+        <v>0.1882</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9297</v>
+        <v>1.8833</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9817</v>
+        <v>1.0213</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3781</v>
+        <v>-0.3566</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3598</v>
+        <v>1.3779</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2111</v>
+        <v>1.0503</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6413</v>
+        <v>0.5448000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5699</v>
+        <v>0.5053</v>
       </c>
       <c r="P7" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2975</v>
+        <v>-1.2673</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8956999999999999</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4018</v>
+        <v>-0.4108</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7194</v>
+        <v>-1.78</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7194</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1432</v>
+        <v>-0.1295</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0339</v>
+        <v>0.0208</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1094</v>
+        <v>-0.1503</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6379</v>
+        <v>0.634</v>
       </c>
       <c r="H8" t="n">
-        <v>1.031</v>
+        <v>1.0458</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3931</v>
+        <v>-0.4118</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9597</v>
+        <v>0.9853</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9597</v>
+        <v>0.9853</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3218</v>
+        <v>-0.3513</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0713</v>
+        <v>0.0605</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3931</v>
+        <v>-0.4118</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0191</v>
+        <v>0.0155</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0067</v>
+        <v>0.0092</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0124</v>
+        <v>0.0063</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2683</v>
+        <v>-0.2959</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0667</v>
+        <v>0.0708</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.335</v>
+        <v>-0.3667</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2618</v>
+        <v>-0.2897</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1312</v>
+        <v>0.1221</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3931</v>
+        <v>-0.4118</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06</v>
+        <v>0.0616</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06</v>
+        <v>0.0616</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3218</v>
+        <v>-0.3513</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0713</v>
+        <v>0.0605</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3931</v>
+        <v>-0.4118</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2065</v>
+        <v>-0.2009</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0067</v>
+        <v>0.0092</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2132</v>
+        <v>-0.2102</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4692</v>
+        <v>-0.4721</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0892</v>
+        <v>-1.0568</v>
       </c>
       <c r="F10" t="n">
-        <v>0.62</v>
+        <v>0.5848</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3181</v>
+        <v>0.2945</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2643</v>
+        <v>-0.2776</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5824</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2781</v>
+        <v>0.254</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2643</v>
+        <v>-0.2776</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5424</v>
+        <v>0.5316</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1872</v>
+        <v>-0.1824</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1289</v>
+        <v>-0.1237</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0583</v>
+        <v>-0.0587</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7801</v>
+        <v>-0.8388</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3439</v>
+        <v>-0.9832000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5638000000000001</v>
+        <v>0.1442999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3582</v>
+        <v>0.3272</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1353</v>
+        <v>-1.1592</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4935</v>
+        <v>1.4863</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6548</v>
+        <v>0.8729</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1906</v>
+        <v>-1.0646</v>
       </c>
       <c r="L11" t="n">
-        <v>1.8455</v>
+        <v>1.9376</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2966</v>
+        <v>-0.5456999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0554</v>
+        <v>-0.0946</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3519000000000001</v>
+        <v>-0.4512</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6001000000000001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6007</v>
+        <v>2.5315</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1415</v>
+        <v>0.133</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1776</v>
+        <v>-0.1366</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3192</v>
+        <v>0.2695</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.88</v>
+        <v>-1.8831</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1795</v>
+        <v>0.2279</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.0595</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="12">
@@ -1345,58 +1345,58 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8375</v>
+        <v>-2.9004</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1223</v>
+        <v>-0.1049</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7151</v>
+        <v>-2.7955</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.657</v>
+        <v>-2.7273</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0084</v>
+        <v>-1.0479</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6485</v>
+        <v>-1.6794</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2</v>
+        <v>0.2042</v>
       </c>
       <c r="K12" t="n">
-        <v>0.12</v>
+        <v>0.1231</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.8569</v>
+        <v>-2.9316</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1284</v>
+        <v>-1.171</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7285</v>
+        <v>-1.7605</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3806</v>
+        <v>-0.3679</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3223</v>
+        <v>-0.3092</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0583</v>
+        <v>-0.0587</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.669899999999999</v>
+        <v>-4.6406</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.0281</v>
+        <v>-5.2963</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3583</v>
+        <v>0.6558</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.8742</v>
+        <v>-2.814</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7995000000000001</v>
+        <v>-0.6756</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.0747</v>
+        <v>-2.1384</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2311</v>
+        <v>0.7355</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7815</v>
+        <v>1.1807</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5504</v>
+        <v>-0.4452</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.1053</v>
+        <v>-3.5495</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5809</v>
+        <v>-1.8563</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.5243</v>
+        <v>-1.6932</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8005</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.0017</v>
+        <v>-5.8421</v>
       </c>
       <c r="R13" t="n">
-        <v>4.2012</v>
+        <v>4.0895</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2046</v>
+        <v>1.1472</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0827</v>
+        <v>0.1413000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>1.122</v>
+        <v>1.0059</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>21.7895</v>
+        <v>21.7646</v>
       </c>
       <c r="E14" t="n">
-        <v>11.7773</v>
+        <v>16.0219</v>
       </c>
       <c r="F14" t="n">
-        <v>10.0121</v>
+        <v>5.7428</v>
       </c>
       <c r="G14" t="n">
-        <v>21.5908</v>
+        <v>21.5734</v>
       </c>
       <c r="H14" t="n">
-        <v>18.0293</v>
+        <v>18.4147</v>
       </c>
       <c r="I14" t="n">
-        <v>3.561500000000001</v>
+        <v>3.158599999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>30.131</v>
+        <v>32.9253</v>
       </c>
       <c r="K14" t="n">
-        <v>19.085</v>
+        <v>21.1697</v>
       </c>
       <c r="L14" t="n">
-        <v>11.0461</v>
+        <v>11.7558</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.539999999999999</v>
+        <v>-11.3521</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0551</v>
+        <v>-2.754899999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.484400000000001</v>
+        <v>-8.597200000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.0002</v>
+        <v>-0.9736999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-27.0077</v>
+        <v>-26.2895</v>
       </c>
       <c r="R14" t="n">
-        <v>26.0074</v>
+        <v>25.31560000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7999</v>
+        <v>2.6439</v>
       </c>
       <c r="T14" t="n">
-        <v>2.258600000000001</v>
+        <v>2.5751</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5416</v>
+        <v>0.06880000000000008</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.6014</v>
+        <v>-1.4789</v>
       </c>
       <c r="W14" t="n">
-        <v>6.395700000000001</v>
+        <v>6.8107</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.9971</v>
+        <v>-8.2896</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BASKONIA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_BASKONIA.xlsx
@@ -565,13 +565,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>12.6434</v>
+        <v>13.2846</v>
       </c>
       <c r="E2" t="n">
-        <v>11.717</v>
+        <v>12.7478</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9263999999999999</v>
+        <v>0.5368999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>5.5075</v>
@@ -610,13 +610,13 @@
         <v>4.089399999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1611</v>
+        <v>0.8024</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0534</v>
+        <v>0.9773999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2146</v>
+        <v>-0.1749000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>4.8326</v>
@@ -643,13 +643,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9331</v>
+        <v>4.893999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>4.697799999999999</v>
+        <v>3.436199999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2352</v>
+        <v>1.4578</v>
       </c>
       <c r="G3" t="n">
         <v>6.7696</v>
@@ -688,13 +688,13 @@
         <v>3.3105</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7339</v>
+        <v>0.6949999999999998</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3018</v>
+        <v>1.0402</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5679</v>
+        <v>-0.3452</v>
       </c>
       <c r="V3" t="n">
         <v>-1.9863</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. SAINSBURY GARCIA</t>
+          <t>M. KHATIASHVILI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7692</v>
+        <v>4.8588</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7971</v>
+        <v>4.9427</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9721</v>
+        <v>-0.08400000000000007</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3076</v>
+        <v>4.231</v>
       </c>
       <c r="H4" t="n">
-        <v>3.788</v>
+        <v>5.0207</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4804</v>
+        <v>-0.7897000000000003</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7915</v>
+        <v>6.2462</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9405</v>
+        <v>6.1401</v>
       </c>
       <c r="L4" t="n">
-        <v>0.851</v>
+        <v>0.1061</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4839</v>
+        <v>-2.0153</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8475</v>
+        <v>-1.1195</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.3314</v>
+        <v>-0.8958</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.7526</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.8947</v>
+        <v>-4.868399999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1421</v>
+        <v>3.8948</v>
       </c>
       <c r="S4" t="n">
-        <v>2.89</v>
+        <v>0.3804</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6792</v>
+        <v>0.5122</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2108</v>
+        <v>-0.1318</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3242</v>
+        <v>1.2211</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2211</v>
+        <v>3.0527</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1031</v>
+        <v>-1.8316</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>4.7498</v>
+        <v>4.5189</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9914999999999999</v>
+        <v>0.8160999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7583</v>
+        <v>3.7027</v>
       </c>
       <c r="G5" t="n">
         <v>5.2615</v>
@@ -844,13 +844,13 @@
         <v>2.1421</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3062</v>
+        <v>0.07519999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3673</v>
+        <v>0.192</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.06110000000000002</v>
+        <v>-0.1167</v>
       </c>
       <c r="V5" t="n">
         <v>-1.9863</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. KHATIASHVILI</t>
+          <t>D. SAINSBURY GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7538</v>
+        <v>3.6844</v>
       </c>
       <c r="E6" t="n">
-        <v>2.9769</v>
+        <v>2.601</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2231000000000001</v>
+        <v>1.0834</v>
       </c>
       <c r="G6" t="n">
-        <v>4.231</v>
+        <v>2.3076</v>
       </c>
       <c r="H6" t="n">
-        <v>5.0207</v>
+        <v>3.788</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7897000000000003</v>
+        <v>-1.4804</v>
       </c>
       <c r="J6" t="n">
-        <v>6.2462</v>
+        <v>3.7915</v>
       </c>
       <c r="K6" t="n">
-        <v>6.1401</v>
+        <v>2.9405</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1061</v>
+        <v>0.851</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0153</v>
+        <v>-1.4839</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1195</v>
+        <v>0.8475</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8958</v>
+        <v>-2.3314</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9737</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.868399999999999</v>
+        <v>-3.8947</v>
       </c>
       <c r="R6" t="n">
-        <v>3.8948</v>
+        <v>2.1421</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.7245</v>
+        <v>1.8053</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.4536</v>
+        <v>1.4832</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2709</v>
+        <v>0.3221000000000001</v>
       </c>
       <c r="V6" t="n">
+        <v>1.3242</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.2211</v>
       </c>
-      <c r="W6" t="n">
-        <v>3.0527</v>
-      </c>
       <c r="X6" t="n">
-        <v>-1.8316</v>
+        <v>0.1031</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1925999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8088</v>
+        <v>-0.4101</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0015</v>
+        <v>1.5302</v>
       </c>
       <c r="G7" t="n">
         <v>2.0715</v>
@@ -1000,13 +1000,13 @@
         <v>2.1421</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2673</v>
+        <v>-0.3399000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8564000000000001</v>
+        <v>-0.4577</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4108</v>
+        <v>0.1178</v>
       </c>
       <c r="V7" t="n">
         <v>-1.78</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1295</v>
+        <v>-0.0236</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0208</v>
+        <v>0.1823</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1503</v>
+        <v>-0.2059</v>
       </c>
       <c r="G8" t="n">
         <v>0.634</v>
@@ -1078,13 +1078,13 @@
         <v>0.1947</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0155</v>
+        <v>0.1214</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0092</v>
+        <v>0.1707</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0063</v>
+        <v>-0.0494</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2959</v>
+        <v>-0.0509</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0708</v>
+        <v>0.2323</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3667</v>
+        <v>-0.2832</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2897</v>
@@ -1156,13 +1156,13 @@
         <v>0.1947</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2009</v>
+        <v>0.0441</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0092</v>
+        <v>0.1707</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2102</v>
+        <v>-0.1267</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4721</v>
+        <v>-0.2611</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0568</v>
+        <v>-0.9571</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5848</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>0.2945</v>
@@ -1234,13 +1234,13 @@
         <v>0.3895</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1824</v>
+        <v>0.0286</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1237</v>
+        <v>-0.024</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0587</v>
+        <v>0.0526</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8388</v>
+        <v>-0.3643000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9832000000000001</v>
+        <v>-0.5364</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1442999999999999</v>
+        <v>0.1721000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0.3272</v>
@@ -1312,13 +1312,13 @@
         <v>2.5315</v>
       </c>
       <c r="S11" t="n">
-        <v>0.133</v>
+        <v>0.6074999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1366</v>
+        <v>0.3102</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2695</v>
+        <v>0.2973</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8831</v>
@@ -1345,13 +1345,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9004</v>
+        <v>-2.4283</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1049</v>
+        <v>0.2559</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7955</v>
+        <v>-2.6842</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7273</v>
@@ -1390,13 +1390,13 @@
         <v>0.1947</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3679</v>
+        <v>0.1043</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3092</v>
+        <v>0.0517</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0587</v>
+        <v>0.05260000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.6406</v>
+        <v>-5.3037</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.2963</v>
+        <v>-5.1247</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6558</v>
+        <v>-0.179</v>
       </c>
       <c r="G13" t="n">
         <v>-2.814</v>
@@ -1468,13 +1468,13 @@
         <v>4.0895</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1472</v>
+        <v>0.484</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1413000000000002</v>
+        <v>0.3129999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0059</v>
+        <v>0.1712</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2211</v>
@@ -1501,19 +1501,19 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>21.7646</v>
+        <v>23.9288</v>
       </c>
       <c r="E14" t="n">
-        <v>16.0219</v>
+        <v>18.186</v>
       </c>
       <c r="F14" t="n">
-        <v>5.7428</v>
+        <v>5.742899999999999</v>
       </c>
       <c r="G14" t="n">
         <v>21.5734</v>
       </c>
       <c r="H14" t="n">
-        <v>18.4147</v>
+        <v>18.41470000000001</v>
       </c>
       <c r="I14" t="n">
         <v>3.158599999999999</v>
@@ -1522,7 +1522,7 @@
         <v>32.9253</v>
       </c>
       <c r="K14" t="n">
-        <v>21.1697</v>
+        <v>21.16970000000001</v>
       </c>
       <c r="L14" t="n">
         <v>11.7558</v>
@@ -1531,7 +1531,7 @@
         <v>-11.3521</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.754899999999999</v>
+        <v>-2.7549</v>
       </c>
       <c r="O14" t="n">
         <v>-8.597200000000001</v>
@@ -1543,22 +1543,22 @@
         <v>-26.2895</v>
       </c>
       <c r="R14" t="n">
-        <v>25.31560000000001</v>
+        <v>25.3156</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6439</v>
+        <v>4.8083</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5751</v>
+        <v>4.7396</v>
       </c>
       <c r="U14" t="n">
-        <v>0.06880000000000008</v>
+        <v>0.06889999999999988</v>
       </c>
       <c r="V14" t="n">
         <v>-1.4789</v>
       </c>
       <c r="W14" t="n">
-        <v>6.8107</v>
+        <v>6.810699999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-8.2896</v>
